--- a/.schema/MSY_KBN_VAL.xlsx
+++ b/.schema/MSY_KBN_VAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395341B4-423F-42CD-BFDD-8D154E51816E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26092B0F-AF79-4434-9D29-1293C4D039AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43200" yWindow="0" windowWidth="14400" windowHeight="15600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MSY_KBN_VAL" sheetId="1" r:id="rId1"/>
@@ -622,15 +622,15 @@
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="6" t="str">
-        <f t="shared" ref="F3:F28" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="str">
-        <f t="shared" ref="H3:H28" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I3" s="4">
         <v>0</v>
@@ -651,15 +651,15 @@
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -680,15 +680,15 @@
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I5" s="4">
         <v>0</v>
@@ -709,15 +709,15 @@
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
@@ -725,28 +725,28 @@
     </row>
     <row r="7" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I7" s="4">
         <v>0</v>
@@ -754,28 +754,28 @@
     </row>
     <row r="8" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D8" s="4">
         <v>2</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -786,25 +786,25 @@
         <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D9" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I9" s="4">
         <v>0</v>
@@ -815,25 +815,25 @@
         <v>16</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I10" s="4">
         <v>0</v>
@@ -844,25 +844,25 @@
         <v>16</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I11" s="4">
         <v>0</v>
@@ -873,25 +873,25 @@
         <v>16</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D12" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
@@ -899,28 +899,28 @@
     </row>
     <row r="13" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D13" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I13" s="4">
         <v>0</v>
@@ -928,28 +928,28 @@
     </row>
     <row r="14" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D14" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -960,25 +960,25 @@
         <v>28</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D15" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I15" s="4">
         <v>0</v>
@@ -986,28 +986,28 @@
     </row>
     <row r="16" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
@@ -1015,28 +1015,28 @@
     </row>
     <row r="17" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D17" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
@@ -1047,25 +1047,25 @@
         <v>29</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I18" s="4">
         <v>0</v>
@@ -1073,26 +1073,28 @@
     </row>
     <row r="19" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="D19" s="4">
+        <v>2</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -1100,26 +1102,28 @@
     </row>
     <row r="20" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="D20" s="4">
+        <v>3</v>
+      </c>
       <c r="E20" s="5"/>
       <c r="F20" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I20" s="4">
         <v>0</v>
@@ -1130,23 +1134,23 @@
         <v>30</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
@@ -1154,26 +1158,26 @@
     </row>
     <row r="22" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I22" s="4">
         <v>0</v>
@@ -1181,26 +1185,26 @@
     </row>
     <row r="23" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I23" s="4">
         <v>0</v>
@@ -1211,23 +1215,23 @@
         <v>34</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I24" s="4">
         <v>0</v>
@@ -1238,23 +1242,23 @@
         <v>34</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I25" s="4">
         <v>0</v>
@@ -1265,23 +1269,23 @@
         <v>34</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I26" s="4">
         <v>0</v>
@@ -1289,28 +1293,26 @@
     </row>
     <row r="27" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G27" s="4">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I27" s="4">
         <v>0</v>
@@ -1318,28 +1320,26 @@
     </row>
     <row r="28" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D28" s="4">
-        <v>2</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="6" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="G28" s="4">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:57:41</v>
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 11:06:49</v>
       </c>
       <c r="I28" s="4">
         <v>0</v>
@@ -1347,6 +1347,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:I24" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I28">
+    <sortCondition ref="A3:A28"/>
+    <sortCondition ref="B3:B28"/>
+  </sortState>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
